--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487447_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487447_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.5877</v>
+        <v>11.2691</v>
       </c>
       <c r="E2" t="n">
-        <v>12.3578</v>
+        <v>11.9055</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7701</v>
+        <v>-0.6364</v>
       </c>
       <c r="G2" t="n">
         <v>4.4596</v>
@@ -610,13 +610,13 @@
         <v>3.1336</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7537</v>
+        <v>0.4351</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3515</v>
+        <v>0.8993</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5978</v>
+        <v>-0.4642</v>
       </c>
       <c r="V2" t="n">
         <v>5.1994</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0706</v>
+        <v>4.0419</v>
       </c>
       <c r="E3" t="n">
-        <v>4.845</v>
+        <v>4.538</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2257</v>
+        <v>-0.4961</v>
       </c>
       <c r="G3" t="n">
         <v>0.3464</v>
@@ -688,13 +688,13 @@
         <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2656</v>
+        <v>0.2369</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7881</v>
+        <v>0.4811</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4775</v>
+        <v>-0.2442</v>
       </c>
       <c r="V3" t="n">
         <v>5.4171</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1127</v>
+        <v>4.0384</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9992</v>
+        <v>4.0586</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1135</v>
+        <v>-0.0202</v>
       </c>
       <c r="G4" t="n">
         <v>2.9967</v>
@@ -766,13 +766,13 @@
         <v>2.9377</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7249</v>
+        <v>0.6506</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6099</v>
+        <v>0.6693</v>
       </c>
       <c r="U4" t="n">
-        <v>0.115</v>
+        <v>-0.0187</v>
       </c>
       <c r="V4" t="n">
         <v>1.3703</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9129</v>
+        <v>3.6932</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8143</v>
+        <v>2.4877</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0986</v>
+        <v>1.2056</v>
       </c>
       <c r="G5" t="n">
         <v>2.9178</v>
@@ -844,13 +844,13 @@
         <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0203</v>
+        <v>-0.24</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.517</v>
+        <v>0.1564</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5033</v>
+        <v>-0.3964</v>
       </c>
       <c r="V5" t="n">
         <v>0.8196</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.673</v>
+        <v>1.6242</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3216</v>
+        <v>0.2192</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3515</v>
+        <v>1.4049</v>
       </c>
       <c r="G6" t="n">
         <v>0.9322</v>
@@ -922,13 +922,13 @@
         <v>1.3709</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0414</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4446</v>
+        <v>0.3423</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.486</v>
+        <v>-0.4326</v>
       </c>
       <c r="V6" t="n">
         <v>0.3905</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0222</v>
+        <v>0.5092</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3037</v>
+        <v>0.5677</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3258</v>
+        <v>-0.0585</v>
       </c>
       <c r="G7" t="n">
         <v>2.1093</v>
@@ -1000,13 +1000,13 @@
         <v>2.546</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8187</v>
+        <v>-0.2873</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.09</v>
+        <v>0.1741</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7287</v>
+        <v>-0.4614</v>
       </c>
       <c r="V7" t="n">
         <v>1.0374</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1923</v>
+        <v>-0.0259</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1174</v>
+        <v>-0.058</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.07489999999999999</v>
+        <v>0.032</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0058</v>
@@ -1078,13 +1078,13 @@
         <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1069</v>
+        <v>0.0594</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1782</v>
+        <v>-0.1188</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0713</v>
+        <v>0.1782</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2754</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4827</v>
+        <v>-0.4293</v>
       </c>
       <c r="E9" t="n">
         <v>-1.5671</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0844</v>
+        <v>1.1379</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0834</v>
@@ -1156,13 +1156,13 @@
         <v>1.7626</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7478</v>
+        <v>-0.6943</v>
       </c>
       <c r="T9" t="n">
         <v>0.1476</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8954</v>
+        <v>-0.8419</v>
       </c>
       <c r="V9" t="n">
         <v>0.5442</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6245</v>
+        <v>-5.2105</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9924</v>
+        <v>-4.6854</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6321</v>
+        <v>-0.5252</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5452</v>
@@ -1234,13 +1234,13 @@
         <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8662</v>
+        <v>-0.4523</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1188</v>
+        <v>0.1882</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7474</v>
+        <v>-0.6405</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8837</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.4804</v>
+        <v>-6.6584</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3288</v>
+        <v>-3.5335</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1516</v>
+        <v>-3.1249</v>
       </c>
       <c r="G11" t="n">
         <v>-4.0446</v>
@@ -1312,13 +1312,13 @@
         <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>0.119</v>
+        <v>-0.059</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7881</v>
+        <v>0.5834</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6691</v>
+        <v>-0.6424</v>
       </c>
       <c r="V11" t="n">
         <v>-2.5549</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>12.5548</v>
+        <v>12.8519</v>
       </c>
       <c r="E12" t="n">
-        <v>13.6359</v>
+        <v>13.9327</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0808</v>
+        <v>-1.080899999999999</v>
       </c>
       <c r="G12" t="n">
         <v>9.083000000000002</v>
@@ -1390,13 +1390,13 @@
         <v>17.6262</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7380999999999994</v>
+        <v>-0.4412000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2258</v>
+        <v>3.5229</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.9639</v>
+        <v>-3.964099999999999</v>
       </c>
       <c r="V12" t="n">
         <v>11.0645</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.0746</v>
+        <v>7.6237</v>
       </c>
       <c r="E13" t="n">
-        <v>8.398400000000001</v>
+        <v>7.7844</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3238</v>
+        <v>-0.1607</v>
       </c>
       <c r="G13" t="n">
         <v>7.5269</v>
@@ -1468,13 +1468,13 @@
         <v>4.1128</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5507</v>
+        <v>0.0998</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2439</v>
+        <v>0.6299</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6932</v>
+        <v>-0.5301</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1781</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7784</v>
+        <v>2.9922</v>
       </c>
       <c r="E14" t="n">
         <v>2.3796</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3987</v>
+        <v>0.6126</v>
       </c>
       <c r="G14" t="n">
         <v>2.2113</v>
@@ -1546,13 +1546,13 @@
         <v>2.3502</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5285</v>
+        <v>-0.3147</v>
       </c>
       <c r="T14" t="n">
         <v>0.4205</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.949</v>
+        <v>-0.7352</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2754</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4474</v>
+        <v>0.4013</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3543</v>
+        <v>0.252</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0931</v>
+        <v>0.1493</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1387</v>
@@ -1624,13 +1624,13 @@
         <v>4.3087</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0412</v>
+        <v>-0.0049</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4846</v>
+        <v>0.3823</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4434</v>
+        <v>-0.3871</v>
       </c>
       <c r="V15" t="n">
         <v>-0.8260999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.036</v>
+        <v>-0.5255</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2103</v>
+        <v>-0.6196</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1743</v>
+        <v>0.0941</v>
       </c>
       <c r="G16" t="n">
         <v>-2.3705</v>
@@ -1702,13 +1702,13 @@
         <v>1.7626</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2757</v>
+        <v>0.7862</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2568</v>
+        <v>0.8475</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0189</v>
+        <v>-0.0613</v>
       </c>
       <c r="V16" t="n">
         <v>0.2754</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4332</v>
+        <v>-1.0306</v>
       </c>
       <c r="E17" t="n">
-        <v>4.2351</v>
+        <v>3.3141</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.6683</v>
+        <v>-4.3447</v>
       </c>
       <c r="G17" t="n">
         <v>1.0945</v>
@@ -1780,13 +1780,13 @@
         <v>2.1543</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1263</v>
+        <v>0.5289</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8203</v>
+        <v>0.8993</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6939</v>
+        <v>-0.3704</v>
       </c>
       <c r="V17" t="n">
         <v>-3.8291</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>A. ALVAREZ JORGE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0759</v>
+        <v>-2</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9443</v>
+        <v>-1.038</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1316</v>
+        <v>-0.9621</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.2291</v>
+        <v>-2.5163</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.475</v>
+        <v>-1.0766</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.7541</v>
+        <v>-1.4397</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.1479</v>
+        <v>-1.2424</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0208</v>
+        <v>-0.6006</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.1687</v>
+        <v>-0.6418</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.0812</v>
+        <v>-1.2739</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4957</v>
+        <v>-0.476</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.5855</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5668</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>3.5253</v>
+        <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7603</v>
+        <v>-0.3086</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1559</v>
+        <v>-0.0329</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9162</v>
+        <v>-0.2757</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8260999999999999</v>
+        <v>1.2166</v>
       </c>
       <c r="W18" t="n">
-        <v>2.318</v>
+        <v>1.2166</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALVAREZ JORGE</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2849</v>
+        <v>-2.274</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2426</v>
+        <v>-1.6372</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0423</v>
+        <v>-0.6367</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5163</v>
+        <v>-5.2291</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0766</v>
+        <v>-0.475</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4397</v>
+        <v>-4.7541</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.2424</v>
+        <v>-2.1479</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6006</v>
+        <v>1.0208</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6418</v>
+        <v>-3.1687</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2739</v>
+        <v>-3.0812</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.476</v>
+        <v>-1.4957</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-1.5855</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3917</v>
+        <v>1.5668</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5875</v>
+        <v>3.5253</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5935</v>
+        <v>0.5623</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2376</v>
+        <v>0.1511</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3559</v>
+        <v>0.4111</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2166</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2166</v>
+        <v>2.318</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7476</v>
+        <v>-3.3649</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7091</v>
+        <v>-2.2998</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0385</v>
+        <v>-1.0652</v>
       </c>
       <c r="G20" t="n">
         <v>-2.2941</v>
@@ -2014,13 +2014,13 @@
         <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2731</v>
+        <v>0.1095</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2023</v>
+        <v>0.207</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0708</v>
+        <v>-0.0975</v>
       </c>
       <c r="V20" t="n">
         <v>-0.397</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.9976</v>
+        <v>-6.1134</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5406</v>
+        <v>-1.9266</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.457</v>
+        <v>-4.1869</v>
       </c>
       <c r="G21" t="n">
         <v>-0.917</v>
@@ -2092,13 +2092,13 @@
         <v>2.7419</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8966</v>
+        <v>-0.0125</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3629</v>
+        <v>0.2511</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5337</v>
+        <v>-0.2636</v>
       </c>
       <c r="V21" t="n">
         <v>-4.9881</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.280099999999999</v>
+        <v>-7.5813</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.6397</v>
+        <v>-5.128</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6404</v>
+        <v>-2.4533</v>
       </c>
       <c r="G22" t="n">
         <v>-6.4499</v>
@@ -2170,13 +2170,13 @@
         <v>1.7626</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7245</v>
+        <v>-0.0257</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3035</v>
+        <v>0.2082</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.421</v>
+        <v>-0.2339</v>
       </c>
       <c r="V22" t="n">
         <v>-1.889</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-12.5549</v>
+        <v>-11.8725</v>
       </c>
       <c r="E23" t="n">
-        <v>1.080800000000001</v>
+        <v>1.0809</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.6358</v>
+        <v>-12.9536</v>
       </c>
       <c r="G23" t="n">
         <v>-9.082899999999999</v>
@@ -2248,19 +2248,19 @@
         <v>24.481</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7379999999999999</v>
+        <v>1.4203</v>
       </c>
       <c r="T23" t="n">
-        <v>3.9639</v>
+        <v>3.964</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.2258</v>
+        <v>-2.543699999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-11.0647</v>
       </c>
       <c r="W23" t="n">
-        <v>2.030199999999999</v>
+        <v>2.0302</v>
       </c>
       <c r="X23" t="n">
         <v>-13.0948</v>
